--- a/data/2025/34-sibiu/143450-sibiu/budget_file.xlsx
+++ b/data/2025/34-sibiu/143450-sibiu/budget_file.xlsx
@@ -1723,39 +1723,32 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>66.02</t>
         </is>
       </c>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>SÄNÄTATE</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n">
+      <c r="E43" t="n">
         <v>5</v>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G43" s="7" t="n"/>
-      <c r="H43" s="7" t="n">
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n">
         <v>16928</v>
       </c>
-      <c r="I43" s="7" t="n"/>
-      <c r="J43" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K43" s="6" t="inlineStr">
-        <is>
-          <t>66.02 total_2026: parent 16.928,00 != sum(children) 9.640,00 (1 children)</t>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -1864,23 +1857,29 @@
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="2" t="inlineStr">
+      <c r="A48" s="6" t="n"/>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>Proiecte cu finanțare din FEN Asistenta sociala</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" s="3" t="n"/>
-      <c r="H48" s="3" t="n">
-        <v>40003</v>
-      </c>
-      <c r="I48" s="3" t="n"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="F48" s="6" t="inlineStr"/>
+      <c r="G48" s="7" t="n"/>
+      <c r="H48" s="7" t="n"/>
+      <c r="I48" s="7" t="n"/>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell '40,00 3,00' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -2154,39 +2153,32 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>67.02</t>
         </is>
       </c>
-      <c r="B57" s="6" t="n"/>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>CULTURA, RELIGIA, ALTE ACTIVITÄTI SPORTIVE SI DE TINERET</t>
         </is>
       </c>
-      <c r="D57" s="6" t="n"/>
-      <c r="E57" s="6" t="n">
+      <c r="E57" t="n">
         <v>6</v>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="n">
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n">
         <v>254712.13</v>
       </c>
-      <c r="I57" s="7" t="n"/>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K57" s="6" t="inlineStr">
-        <is>
-          <t>67.02 total_2026: parent 254.712,13 != sum(children) 528,00 (1 children)</t>
+      <c r="I57" s="3" t="n"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -2657,23 +2649,29 @@
       </c>
     </row>
     <row r="73">
-      <c r="C73" s="2" t="inlineStr">
+      <c r="A73" s="6" t="n"/>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>Intretinere gradini publice, baze sportive si de agrement Alte cheltuieli in domeniile culturii, recreerii si religiei</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" s="3" t="n"/>
-      <c r="H73" s="3" t="n">
-        <v>104627445000</v>
-      </c>
-      <c r="I73" s="3" t="n"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="F73" s="6" t="inlineStr"/>
+      <c r="G73" s="7" t="n"/>
+      <c r="H73" s="7" t="n"/>
+      <c r="I73" s="7" t="n"/>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell '104.627,44 5.000,00' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -10766,39 +10764,37 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="4" t="inlineStr">
+      <c r="A348" s="6" t="inlineStr">
         <is>
           <t>68.02.04</t>
         </is>
       </c>
-      <c r="B348" s="4" t="n"/>
-      <c r="C348" s="4" t="inlineStr">
+      <c r="B348" s="6" t="n"/>
+      <c r="C348" s="6" t="inlineStr">
         <is>
           <t>Total capitol ,din care :</t>
         </is>
       </c>
-      <c r="D348" s="4" t="n"/>
-      <c r="E348" s="4" t="n">
+      <c r="D348" s="6" t="n"/>
+      <c r="E348" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="F348" s="4" t="inlineStr">
+      <c r="F348" s="6" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G348" s="5" t="n"/>
-      <c r="H348" s="5" t="n">
-        <v>98416405499</v>
-      </c>
-      <c r="I348" s="5" t="n"/>
-      <c r="J348" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K348" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (40%): 'Total capitol ,din care :' vs 'Asistenta acordata persoanelor in varsta'</t>
+      <c r="G348" s="7" t="n"/>
+      <c r="H348" s="7" t="n"/>
+      <c r="I348" s="7" t="n"/>
+      <c r="J348" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K348" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell '98.416,40 5.499,00' in column total_2026; name mismatch vs nomenclator (40%): 'Total capitol ,din care :' vs 'Asistenta acordata persoanelor in varsta'</t>
         </is>
       </c>
     </row>
@@ -18340,39 +18336,37 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" s="4" t="inlineStr">
+      <c r="A614" s="6" t="inlineStr">
         <is>
           <t>70.02.50</t>
         </is>
       </c>
-      <c r="B614" s="4" t="n"/>
-      <c r="C614" s="4" t="inlineStr">
+      <c r="B614" s="6" t="n"/>
+      <c r="C614" s="6" t="inlineStr">
         <is>
           <t>Total capitol ,din care :</t>
         </is>
       </c>
-      <c r="D614" s="4" t="n"/>
-      <c r="E614" s="4" t="n">
+      <c r="D614" s="6" t="n"/>
+      <c r="E614" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="F614" s="4" t="inlineStr">
+      <c r="F614" s="6" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G614" s="5" t="n"/>
-      <c r="H614" s="5" t="n">
-        <v>155698457222</v>
-      </c>
-      <c r="I614" s="5" t="n"/>
-      <c r="J614" s="4" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-      <c r="K614" s="4" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (26%): 'Total capitol ,din care :' vs 'Alte servicii în domeniile locuintelor, '</t>
+      <c r="G614" s="7" t="n"/>
+      <c r="H614" s="7" t="n"/>
+      <c r="I614" s="7" t="n"/>
+      <c r="J614" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="K614" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell '155.698,45 7.222,00' in column total_2026; name mismatch vs nomenclator (26%): 'Total capitol ,din care :' vs 'Alte servicii în domeniile locuintelor, '</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:F173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -20900,7 +20894,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -20913,24 +20907,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>54.02</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>51.02.10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 54.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (30%): 'Cheltuieli de personal' vs 'Plati in contul creditelor garantate si/'</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -20943,24 +20932,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>51.02.20</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 66.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (32%): 'Cheltuieli materiale și servicii' vs 'Subprogramul privind alimentarea cu apă '</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -20969,28 +20953,23 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>51.02.01.03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 67.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (29%): 'Primăria' vs 'Autoritati executive'</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -20999,28 +20978,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>51.02.01.03</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 68.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (29%): 'Direcția Fiscală Locală Sibiu' vs 'Autoritati executive'</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -21029,41 +21003,36 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>51.02.01.03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 74.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>83.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -21073,14 +21042,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 83.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>54.02 total_2026: parent 6.871,00 != sum(children) 200,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -21089,28 +21058,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>54.02.10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 84.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (36%): 'Cheltuieli personal' vs 'Servicii publice comunitare de evidenţă '</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -21119,28 +21083,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>54.02</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>54.02.50</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 54.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (38%): 'Fonduri de rezerva' vs 'Alte servicii publice generale'</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -21149,28 +21108,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>54.02.10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 66.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -21179,48 +21133,48 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>54.02.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 68.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>54.02.50</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p6: 0 cells recovered</t>
+          <t>name mismatch vs nomenclator (38%): 'SP Administrare Cimitir' vs 'Alte servicii publice generale'</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -21233,12 +21187,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>51.02.10</t>
+          <t>54.02.50</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): 'Cheltuieli de personal' vs 'Plati in contul creditelor garantate si/'</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
@@ -21258,37 +21212,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>51.02.20</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Cheltuieli materiale și servicii' vs 'Subprogramul privind alimentarea cu apă '</t>
+          <t>name mismatch vs nomenclator (25%): 'DOBÂNZI' vs 'Tranzactii privind datoria publica si im'</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>51.02.01.03</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Primăria' vs 'Autoritati executive'</t>
+          <t>unparseable cell '40,00 3,00' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -21304,16 +21258,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>51.02.01.03</t>
+          <t>66.02.06.01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Direcția Fiscală Locală Sibiu' vs 'Autoritati executive'</t>
+          <t>name mismatch vs nomenclator (50%): 'Agenda Sănătății' vs 'Spitale generale'</t>
         </is>
       </c>
     </row>
@@ -21329,46 +21283,41 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>51.02.01.03</t>
+          <t>66.02.06.01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>54.02</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>66.02.08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>54.02 total_2026: parent 6.871,00 != sum(children) 200,00 (4 children)</t>
+          <t>name mismatch vs nomenclator (32%): 'Învățământ' vs 'Servicii de sanatate publica'</t>
         </is>
       </c>
     </row>
@@ -21384,23 +21333,23 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>54.02.10</t>
+          <t>66.02.08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Cheltuieli personal' vs 'Servicii publice comunitare de evidenţă '</t>
+          <t>name mismatch vs nomenclator (46%): 'Direcția de Asistență Socială' vs 'Servicii de sanatate publica'</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -21409,23 +21358,23 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>54.02.50</t>
+          <t>66.02.08</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'Fonduri de rezerva' vs 'Alte servicii publice generale'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -21434,23 +21383,23 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>54.02.10</t>
+          <t>66.02.50.50</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>name mismatch vs nomenclator (40%): 'Direcția de Asistență socială - Centru t' vs 'Alte institutii si actiuni sanitare'</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -21459,23 +21408,23 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>54.02.50</t>
+          <t>66.02.50.50</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>name mismatch vs nomenclator (19%): 'Primăria' vs 'Alte institutii si actiuni sanitare'</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -21484,23 +21433,23 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>54.02.50</t>
+          <t>66.02.50.50</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'SP Administrare Cimitir' vs 'Alte servicii publice generale'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -21509,16 +21458,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>54.02.50</t>
+          <t>67.02.03.04</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>name mismatch vs nomenclator (29%): 'Teatru Radu Stanca' vs 'Institutii publice de spectacole si conc'</t>
         </is>
       </c>
     </row>
@@ -21534,46 +21483,41 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>67.02.03.04</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (25%): 'DOBÂNZI' vs 'Tranzactii privind datoria publica si im'</t>
+          <t>name mismatch vs nomenclator (25%): 'Teatrul Gong' vs 'Institutii publice de spectacole si conc'</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>67.02.03.04</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>66.02 total_2026: parent 16.928,00 != sum(children) 9.640,00 (1 children)</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -21593,19 +21537,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>66.02.06.01</t>
+          <t>67.02.05.03</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (50%): 'Agenda Sănătății' vs 'Spitale generale'</t>
+          <t>name mismatch vs nomenclator (38%): 'SP Managementul Integrat pentru Ecosiste' vs 'Intretinere gradini publice, parcuri, zo'</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -21618,19 +21562,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>66.02.06.01</t>
+          <t>67.02.05.03</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Intretinere gradini publice, parcuri, zo'</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -21643,19 +21587,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>66.02.08</t>
+          <t>67.02.05.03</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Învățământ' vs 'Servicii de sanatate publica'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -21668,19 +21612,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>66.02.08</t>
+          <t>67.02.05.03</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (46%): 'Direcția de Asistență Socială' vs 'Servicii de sanatate publica'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -21693,12 +21637,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>66.02.08</t>
+          <t>67.02.05.01</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (31%): 'Finanțare programe sportive' vs 'Sport'</t>
         </is>
       </c>
     </row>
@@ -21718,19 +21662,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>66.02.50.50</t>
+          <t>67.02.05.01</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (40%): 'Direcția de Asistență socială - Centru t' vs 'Alte institutii si actiuni sanitare'</t>
+          <t>name mismatch vs nomenclator (23%): 'Finantarea cluburilor sportive publice' vs 'Sport'</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -21743,12 +21687,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>66.02.50.50</t>
+          <t>67.02.05.01</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (19%): 'Primăria' vs 'Alte institutii si actiuni sanitare'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -21758,34 +21702,34 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>6</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>66.02.50.50</t>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>unparseable cell '104.627,44 5.000,00' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -21793,17 +21737,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>67.02.50</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>67.02 total_2026: parent 254.712,13 != sum(children) 528,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (44%): 'Agenda comunitatii și de tineret' vs 'Alte servicii în domeniile culturii, rec'</t>
         </is>
       </c>
     </row>
@@ -21823,19 +21762,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>67.02.03.04</t>
+          <t>67.02.05.02</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Teatru Radu Stanca' vs 'Institutii publice de spectacole si conc'</t>
+          <t>name mismatch vs nomenclator (26%): 'Fond destinat activității de tineret, di' vs 'Tineret'</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -21848,19 +21787,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>67.02.03.04</t>
+          <t>67.02.05.02</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (25%): 'Teatrul Gong' vs 'Institutii publice de spectacole si conc'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -21873,19 +21812,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>67.02.03.04</t>
+          <t>67.02.05.02</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (23%): 'Agenda educațională' vs 'Tineret'</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -21898,19 +21837,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>67.02.05.03</t>
+          <t>67.02.05.02</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'SP Managementul Integrat pentru Ecosiste' vs 'Intretinere gradini publice, parcuri, zo'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -21923,24 +21862,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>67.02.05.03</t>
+          <t>67.02.05.02</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Intretinere gradini publice, parcuri, zo'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -21948,19 +21887,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>67.02.05.03</t>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>68.02 total_2026: parent 98.550,40 != sum(children) 38.424,80 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -21973,12 +21917,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>67.02.05.03</t>
+          <t>68.02.10</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (39%): 'Cheltuieli de personal' vs 'Ajutoare pentru locuinte'</t>
         </is>
       </c>
     </row>
@@ -21998,12 +21942,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>67.02.05.01</t>
+          <t>68.02.04</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'Finanțare programe sportive' vs 'Sport'</t>
+          <t>name mismatch vs nomenclator (54%): 'Asistenta Sociala - Căminul pentru perso' vs 'Asistenta acordata persoanelor in varsta'</t>
         </is>
       </c>
     </row>
@@ -22023,19 +21967,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>67.02.05.01</t>
+          <t>68.02.05.02</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (23%): 'Finantarea cluburilor sportive publice' vs 'Sport'</t>
+          <t>name mismatch vs nomenclator (48%): 'Drepturile persoanelor si asistentilor p' vs 'Asistenta sociala  in  caz de invalidita'</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -22048,19 +21992,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>67.02.05.01</t>
+          <t>68.02.50.50</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (55%): 'Alte ajutoare sociale - Primaria' vs 'Alte cheltuieli in domeniul asistentei s'</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -22073,44 +22017,44 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>67.02.50</t>
+          <t>68.02.50.50</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (44%): 'Agenda comunitatii și de tineret' vs 'Alte servicii în domeniile culturii, rec'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>6</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>67.02.05.02</t>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (26%): 'Fond destinat activității de tineret, di' vs 'Tineret'</t>
+          <t>unparseable cell '65.606,05 203.033,61' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -22123,19 +22067,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>67.02.05.02</t>
+          <t>70.02.50</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (43%): 'Total capitol ,din care : SP Salubrizare' vs 'Alte servicii în domeniile locuintelor, '</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -22144,23 +22088,23 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>67.02.05.02</t>
+          <t>70.02.50</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (23%): 'Agenda educațională' vs 'Tineret'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -22169,16 +22113,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>67.02.05.02</t>
+          <t>70.02.50</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (48%): 'Alte subventii si transferuri pentru inv' vs 'Alte servicii în domeniile locuintelor, '</t>
         </is>
       </c>
     </row>
@@ -22194,11 +22138,11 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>67.02.05.02</t>
+          <t>70.02.50</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -22219,11 +22163,11 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -22233,7 +22177,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>68.02 total_2026: parent 98.550,40 != sum(children) 38.424,80 (3 children)</t>
+          <t>74.02 total_2026: parent 147.146,20 != sum(children) 5.266,08 (3 children)</t>
         </is>
       </c>
     </row>
@@ -22249,23 +22193,23 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>68.02.10</t>
+          <t>74.02.05.01</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'Cheltuieli de personal' vs 'Ajutoare pentru locuinte'</t>
+          <t>name mismatch vs nomenclator (23%): 'SP Salubrizare, Protecția Mediului și Ad' vs 'Salubritate'</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -22274,16 +22218,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>68.02.04</t>
+          <t>74.02.05.01</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (54%): 'Asistenta Sociala - Căminul pentru perso' vs 'Asistenta acordata persoanelor in varsta'</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -22299,73 +22243,83 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>68.02.05.02</t>
+          <t>74.02.06</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (48%): 'Drepturile persoanelor si asistentilor p' vs 'Asistenta sociala  in  caz de invalidita'</t>
+          <t>name mismatch vs nomenclator (40%): 'Canalizare' vs 'Canalizarea si tratarea apelor reziduale'</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>68.02.50.50</t>
+          <t>83.02</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (55%): 'Alte ajutoare sociale - Primaria' vs 'Alte cheltuieli in domeniul asistentei s'</t>
+          <t>83.02 total_2026: parent 1.380,00 != sum(children) 70,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>68.02.50.50</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>84.02 total_2026: parent 340.850,17 != sum(children) 33.350,77 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -22374,123 +22328,123 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>8</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>02</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>unparseable cell '65.606,05 203.033,61' in column total_2026</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>70.02.50</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (43%): 'Total capitol ,din care : SP Salubrizare' vs 'Alte servicii în domeniile locuintelor, '</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>70.02.50</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>70.02.50</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (48%): 'Alte subventii si transferuri pentru inv' vs 'Alte servicii în domeniile locuintelor, '</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>70.02.50</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -22499,156 +22453,141 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>74.02 total_2026: parent 147.146,20 != sum(children) 5.266,08 (3 children)</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>74.02.05.01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (23%): 'SP Salubrizare, Protecția Mediului și Ad' vs 'Salubritate'</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>74.02.05.01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>74.02.06</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (40%): 'Canalizare' vs 'Canalizarea si tratarea apelor reziduale'</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>83.02</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>40.02.14</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>83.02 total_2026: parent 1.380,00 != sum(children) 70,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Sume din excedentul bugetului local util'</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>42.02.88</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>84.02 total_2026: parent 340.850,17 != sum(children) 33.350,77 (1 children)</t>
+          <t>name mismatch vs nomenclator (21%): 'Anghel Saligny"' vs 'Alocări de sume din PNRR aferente asiste'</t>
         </is>
       </c>
     </row>
@@ -22664,7 +22603,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -22680,25 +22619,25 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>45.02.48.01</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (52%): '-Sume de la UE pentru FEDR an curent' vs 'Sume primite în contul plăţilor efectuat'</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22653,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -22730,25 +22669,25 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>48.02.01.01</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (52%): '-Sume de la UE pentru FEDR an curent' vs 'Sume primite in contul platilor efectuat'</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22703,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -22780,107 +22719,107 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>51.02.10</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (30%): 'Cheltuieli de personal' vs 'Plati in contul creditelor garantate si/'</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>51.02.20</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (32%): 'Cheltuieli materiale și servicii' vs 'Subprogramul privind alimentarea cu apă '</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>51.02.01.03</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (29%): 'Primăria' vs 'Autoritati executive'</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>51.02.01.03</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (29%): 'Direcția Fiscală Locală Sibiu' vs 'Autoritati executive'</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -22889,66 +22828,71 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>40.02.14</t>
+          <t>51.02.01.03</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Sume din excedentul bugetului local util'</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>42.02.88</t>
+          <t>54.02</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (21%): 'Anghel Saligny"' vs 'Alocări de sume din PNRR aferente asiste'</t>
+          <t>54.02 total_2026: parent 6.084,00 != sum(children) 200,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>54.02.10</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (36%): 'Cheltuieli personal' vs 'Servicii publice comunitare de evidenţă '</t>
         </is>
       </c>
     </row>
@@ -22964,48 +22908,48 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>45.02.48.01</t>
+          <t>54.02.50</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (52%): '-Sume de la UE pentru FEDR an curent' vs 'Sume primite în contul plăţilor efectuat'</t>
+          <t>name mismatch vs nomenclator (38%): 'Fonduri de rezerva' vs 'Alte servicii publice generale'</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>54.02.10</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -23014,48 +22958,48 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>48.02.01.01</t>
+          <t>54.02.50</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (52%): '-Sume de la UE pentru FEDR an curent' vs 'Sume primite in contul platilor efectuat'</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>54.02.50</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (38%): 'SP Administrare Cimitir' vs 'Alte servicii publice generale'</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -23068,12 +23012,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>51.02.10</t>
+          <t>54.02.50</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): 'Cheltuieli de personal' vs 'Plati in contul creditelor garantate si/'</t>
+          <t>duplicate of p11 with different values</t>
         </is>
       </c>
     </row>
@@ -23093,24 +23037,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>51.02.20</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Cheltuieli materiale și servicii' vs 'Subprogramul privind alimentarea cu apă '</t>
+          <t>name mismatch vs nomenclator (25%): 'DOBÂNZI' vs 'Tranzactii privind datoria publica si im'</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -23118,12 +23062,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>51.02.01.03</t>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Primăria' vs 'Autoritati executive'</t>
+          <t>66.02 total_2026: parent 16.888,00 != sum(children) 9.640,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -23139,16 +23088,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>51.02.01.03</t>
+          <t>66.02.06.01</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Direcția Fiscală Locală Sibiu' vs 'Autoritati executive'</t>
+          <t>name mismatch vs nomenclator (50%): 'Agenda Sănătății' vs 'Spitale generale'</t>
         </is>
       </c>
     </row>
@@ -23164,46 +23113,41 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>51.02.01.03</t>
+          <t>66.02.06.01</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>54.02</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>66.02.08</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>54.02 total_2026: parent 6.084,00 != sum(children) 200,00 (4 children)</t>
+          <t>name mismatch vs nomenclator (32%): 'Învățământ' vs 'Servicii de sanatate publica'</t>
         </is>
       </c>
     </row>
@@ -23219,23 +23163,23 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>54.02.10</t>
+          <t>66.02.08</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Cheltuieli personal' vs 'Servicii publice comunitare de evidenţă '</t>
+          <t>name mismatch vs nomenclator (46%): 'Direcția de Asistență Socială' vs 'Servicii de sanatate publica'</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -23244,23 +23188,23 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>54.02.50</t>
+          <t>66.02.08</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'Fonduri de rezerva' vs 'Alte servicii publice generale'</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -23269,23 +23213,23 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>54.02.10</t>
+          <t>66.02.50.50</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>name mismatch vs nomenclator (40%): 'Direcția de Asistență socială - Centru t' vs 'Alte institutii si actiuni sanitare'</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -23294,23 +23238,23 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>54.02.50</t>
+          <t>66.02.50.50</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>name mismatch vs nomenclator (19%): 'Primăria' vs 'Alte institutii si actiuni sanitare'</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -23319,23 +23263,23 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>54.02.50</t>
+          <t>66.02.50.50</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'SP Administrare Cimitir' vs 'Alte servicii publice generale'</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -23344,16 +23288,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>54.02.50</t>
+          <t>67.02.03.04</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>duplicate of p11 with different values</t>
+          <t>name mismatch vs nomenclator (29%): 'Teatru Radu Stanca' vs 'Institutii publice de spectacole si conc'</t>
         </is>
       </c>
     </row>
@@ -23369,46 +23313,41 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>67.02.03.04</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (25%): 'DOBÂNZI' vs 'Tranzactii privind datoria publica si im'</t>
+          <t>name mismatch vs nomenclator (25%): 'Teatrul Gong' vs 'Institutii publice de spectacole si conc'</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>67.02.03.04</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>66.02 total_2026: parent 16.888,00 != sum(children) 9.640,00 (1 children)</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
@@ -23428,19 +23367,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>66.02.06.01</t>
+          <t>67.02.03.30</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (50%): 'Agenda Sănătății' vs 'Spitale generale'</t>
+          <t>name mismatch vs nomenclator (31%): 'SP Managementul Integrat pentru Ecosiste' vs 'Alte servicii culturale'</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -23453,19 +23392,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>66.02.06.01</t>
+          <t>67.02.05.03</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Intretinere gradini publice, parcuri, zo'</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -23478,19 +23417,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>66.02.08</t>
+          <t>67.02.05.03</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Învățământ' vs 'Servicii de sanatate publica'</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -23503,19 +23442,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>66.02.08</t>
+          <t>67.02.03.30</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (46%): 'Direcția de Asistență Socială' vs 'Servicii de sanatate publica'</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -23528,19 +23467,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>66.02.08</t>
+          <t>67.02.05.01</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>name mismatch vs nomenclator (23%): 'Finantarea cluburilor sportive publice' vs 'Sport'</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -23553,12 +23492,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>66.02.50.50</t>
+          <t>67.02.05.03</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (40%): 'Direcția de Asistență socială - Centru t' vs 'Alte institutii si actiuni sanitare'</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
@@ -23578,12 +23517,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>66.02.50.50</t>
+          <t>67.02.50</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (19%): 'Primăria' vs 'Alte institutii si actiuni sanitare'</t>
+          <t>name mismatch vs nomenclator (26%): 'Agenda comunitatii' vs 'Alte servicii în domeniile culturii, rec'</t>
         </is>
       </c>
     </row>
@@ -23603,7 +23542,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>66.02.50.50</t>
+          <t>67.02.50</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -23628,19 +23567,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>67.02.03.04</t>
+          <t>67.02.05.02</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Teatru Radu Stanca' vs 'Institutii publice de spectacole si conc'</t>
+          <t>name mismatch vs nomenclator (26%): 'Fond destinat activității de tineret, di' vs 'Tineret'</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -23653,19 +23592,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>67.02.03.04</t>
+          <t>67.02.05.02</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (25%): 'Teatrul Gong' vs 'Institutii publice de spectacole si conc'</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -23678,19 +23617,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>67.02.03.04</t>
+          <t>67.02.05.02</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>name mismatch vs nomenclator (23%): 'Agenda educațională' vs 'Tineret'</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -23703,19 +23642,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>67.02.03.30</t>
+          <t>67.02.05.02</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'SP Managementul Integrat pentru Ecosiste' vs 'Alte servicii culturale'</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -23728,24 +23667,24 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>67.02.05.03</t>
+          <t>67.02.05.02</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Intretinere gradini publice, parcuri, zo'</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -23753,19 +23692,24 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>67.02.05.03</t>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>68.02 total_2026: parent 98.416,40 != sum(children) 31.833,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -23778,44 +23722,44 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>67.02.03.30</t>
+          <t>68.02.10</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>name mismatch vs nomenclator (39%): 'Cheltuieli de personal' vs 'Ajutoare pentru locuinte'</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C114" t="n">
         <v>12</v>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>67.02.05.01</t>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (23%): 'Finantarea cluburilor sportive publice' vs 'Sport'</t>
+          <t>unparseable cell '98.416,40 5.499,00' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -23828,12 +23772,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>67.02.05.03</t>
+          <t>68.02.04</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>name mismatch vs nomenclator (40%): 'Total capitol ,din care :' vs 'Asistenta acordata persoanelor in varsta'</t>
         </is>
       </c>
     </row>
@@ -23853,12 +23797,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>67.02.50</t>
+          <t>68.02.50.50</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (26%): 'Agenda comunitatii' vs 'Alte servicii în domeniile culturii, rec'</t>
+          <t>name mismatch vs nomenclator (55%): 'Alte ajutoare sociale - Primaria' vs 'Alte cheltuieli in domeniul asistentei s'</t>
         </is>
       </c>
     </row>
@@ -23878,7 +23822,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>67.02.50</t>
+          <t>68.02.50.50</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -23903,19 +23847,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>67.02.05.02</t>
+          <t>70.02.06</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (26%): 'Fond destinat activității de tineret, di' vs 'Tineret'</t>
+          <t>name mismatch vs nomenclator (36%): 'luminat' vs 'Iluminat public si electrificari'</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -23924,23 +23868,23 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>67.02.05.02</t>
+          <t>70.02.50</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>name mismatch vs nomenclator (48%): 'Alte subventii si transferuri pentru inv' vs 'Alte servicii în domeniile locuintelor, '</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -23949,23 +23893,23 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>67.02.05.02</t>
+          <t>70.02.50</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (23%): 'Agenda educațională' vs 'Tineret'</t>
+          <t>duplicate of p13 with different values</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -23974,16 +23918,16 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>67.02.05.02</t>
+          <t>74.02.05.01</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>name mismatch vs nomenclator (23%): 'SP Salubrizare, Protecția Mediului și Ad' vs 'Salubritate'</t>
         </is>
       </c>
     </row>
@@ -23999,46 +23943,41 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>67.02.05.02</t>
+          <t>74.02.05.01</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>duplicate of p13 with different values</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>74.02.06</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>68.02 total_2026: parent 98.416,40 != sum(children) 31.833,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (40%): 'Canalizare' vs 'Canalizarea si tratarea apelor reziduale'</t>
         </is>
       </c>
     </row>
@@ -24054,16 +23993,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>68.02.10</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'Cheltuieli de personal' vs 'Ajutoare pentru locuinte'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Alte impozite si taxe fiscale'</t>
         </is>
       </c>
     </row>
@@ -24079,141 +24018,141 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>68.02.04</t>
+          <t>35.02.03</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (40%): 'Total capitol ,din care :' vs 'Asistenta acordata persoanelor in varsta'</t>
+          <t>name mismatch vs nomenclator (26%): 'rnnfi~r::irP::i ootrivit IPP ii I' vs 'Incasari din valorificarea bunurilor con'</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>68.02.50.50</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (55%): 'Alte ajutoare sociale - Primaria' vs 'Alte cheltuieli in domeniul asistentei s'</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>68.02.50.50</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>70.02.06</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'luminat' vs 'Iluminat public si electrificari'</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>70.02.50</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (48%): 'Alte subventii si transferuri pentru inv' vs 'Alte servicii în domeniile locuintelor, '</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>70.02.50</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>duplicate of p13 with different values</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -24229,23 +24168,23 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>74.02.05.01</t>
+          <t>42.02.66</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (23%): 'SP Salubrizare, Protecția Mediului și Ad' vs 'Salubritate'</t>
+          <t>name mismatch vs nomenclator (13%): '1publică' vs 'Subvenţii din bugetul de stat alocate co'</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -24254,41 +24193,41 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>74.02.05.01</t>
+          <t>42.02.87</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>duplicate of p13 with different values</t>
+          <t>name mismatch vs nomenclator (20%): ',Anghel Salignv"' vs 'Subvenții de la bugetul de stat către bu'</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>74.02.06</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (40%): 'Canalizare' vs 'Canalizarea si tratarea apelor reziduale'</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -24304,16 +24243,16 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>51.02.20</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Alte impozite si taxe fiscale'</t>
+          <t>name mismatch vs nomenclator (32%): 'Cheltuieli materiale servicii şi' vs 'Subprogramul privind alimentarea cu apă '</t>
         </is>
       </c>
     </row>
@@ -24329,41 +24268,41 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>35.02.03</t>
+          <t>51.02.01.03</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (26%): 'rnnfi~r::irP::i ootrivit IPP ii I' vs 'Incasari din valorificarea bunurilor con'</t>
+          <t>name mismatch vs nomenclator (29%): 'Primăria' vs 'Autoritati executive'</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>51.02.01.03</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (29%): 'Sibiu Direcţia Fiscală Locală' vs 'Autoritati executive'</t>
         </is>
       </c>
     </row>
@@ -24379,7 +24318,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -24395,50 +24334,50 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>54.02.10</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (36%): 'Cheltuieli personal' vs 'Servicii publice comunitare de evidenţă '</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B139" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>54.02.50</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (38%): 'SP Administrare Cimitir' vs 'Alte servicii publice generale'</t>
         </is>
       </c>
     </row>
@@ -24454,7 +24393,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -24470,50 +24409,50 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>42.02.66</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (13%): '1publică' vs 'Subvenţii din bugetul de stat alocate co'</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>42.02.87</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (20%): ',Anghel Salignv"' vs 'Subvenții de la bugetul de stat către bu'</t>
+          <t>code 02 (expense_economic) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -24529,7 +24468,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -24554,23 +24493,23 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>51.02.20</t>
+          <t>66.02.06.01</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Cheltuieli materiale servicii şi' vs 'Subprogramul privind alimentarea cu apă '</t>
+          <t>name mismatch vs nomenclator (50%): 'Agenda Sănătății' vs 'Spitale generale'</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -24579,16 +24518,16 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>51.02.01.03</t>
+          <t>66.02.06.01</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Primăria' vs 'Autoritati executive'</t>
+          <t>duplicate of p18 with different values</t>
         </is>
       </c>
     </row>
@@ -24604,41 +24543,41 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>51.02.01.03</t>
+          <t>66.02.08</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Sibiu Direcţia Fiscală Locală' vs 'Autoritati executive'</t>
+          <t>name mismatch vs nomenclator (32%): 'Învățământ' vs 'Servicii de sanatate publica'</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B147" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>66.02.08</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (46%): 'Direcția de Asistență Socială' vs 'Servicii de sanatate publica'</t>
         </is>
       </c>
     </row>
@@ -24654,16 +24593,16 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>54.02.10</t>
+          <t>66.02.50.50</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Cheltuieli personal' vs 'Servicii publice comunitare de evidenţă '</t>
+          <t>name mismatch vs nomenclator (40%): 'Direcția de Asistență socială - Centru t' vs 'Alte institutii si actiuni sanitare'</t>
         </is>
       </c>
     </row>
@@ -24679,123 +24618,123 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>54.02.50</t>
+          <t>66.02.50.50</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'SP Administrare Cimitir' vs 'Alte servicii publice generale'</t>
+          <t>name mismatch vs nomenclator (19%): 'Primăria' vs 'Alte institutii si actiuni sanitare'</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>66.02.50.50</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>duplicate of p18 with different values</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (52%): 'CULTURA, RELIGIA, ALTE ACTIVITATI SPORTI' vs 'Cultura, recreere si religie'</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>67.02.03.04</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (29%): 'Teatru Radu Stanca' vs 'Institutii publice de spectacole si conc'</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>67.02.03.04</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>code 02 (expense_economic) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (25%): 'Teatrul Gong' vs 'Institutii publice de spectacole si conc'</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -24808,19 +24747,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>66.02.06.01</t>
+          <t>67.02.03.04</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (50%): 'Agenda Sănătății' vs 'Spitale generale'</t>
+          <t>duplicate of p18 with different values</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -24833,12 +24772,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>66.02.06.01</t>
+          <t>67.02.03.30</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>duplicate of p18 with different values</t>
+          <t>name mismatch vs nomenclator (31%): 'SP Managementul Integrat pentru Ecosiste' vs 'Alte servicii culturale'</t>
         </is>
       </c>
     </row>
@@ -24858,19 +24797,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>66.02.08</t>
+          <t>67.02.05.03</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Învățământ' vs 'Servicii de sanatate publica'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Intretinere gradini publice, parcuri, zo'</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -24883,12 +24822,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>66.02.08</t>
+          <t>67.02.05.03</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (46%): 'Direcția de Asistență Socială' vs 'Servicii de sanatate publica'</t>
+          <t>duplicate of p18 with different values</t>
         </is>
       </c>
     </row>
@@ -24908,12 +24847,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>66.02.50.50</t>
+          <t>67.02.05.01</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (40%): 'Direcția de Asistență socială - Centru t' vs 'Alte institutii si actiuni sanitare'</t>
+          <t>name mismatch vs nomenclator (31%): 'Finanțare programe sportive' vs 'Sport'</t>
         </is>
       </c>
     </row>
@@ -24933,19 +24872,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>66.02.50.50</t>
+          <t>67.02.50</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (19%): 'Primăria' vs 'Alte institutii si actiuni sanitare'</t>
+          <t>name mismatch vs nomenclator (26%): 'Agenda comunitatii' vs 'Alte servicii în domeniile culturii, rec'</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -24958,12 +24897,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>66.02.50.50</t>
+          <t>67.02.05.02</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>duplicate of p18 with different values</t>
+          <t>name mismatch vs nomenclator (26%): 'Fond destinat activității de tineret, di' vs 'Tineret'</t>
         </is>
       </c>
     </row>
@@ -24983,12 +24922,12 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>67.02.05.02</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (52%): 'CULTURA, RELIGIA, ALTE ACTIVITATI SPORTI' vs 'Cultura, recreere si religie'</t>
+          <t>name mismatch vs nomenclator (23%): 'Agenda educațională' vs 'Tineret'</t>
         </is>
       </c>
     </row>
@@ -25008,12 +24947,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>67.02.03.04</t>
+          <t>68.02.10</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Teatru Radu Stanca' vs 'Institutii publice de spectacole si conc'</t>
+          <t>name mismatch vs nomenclator (39%): 'Cheltuieli de personal' vs 'Ajutoare pentru locuinte'</t>
         </is>
       </c>
     </row>
@@ -25033,19 +24972,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>67.02.03.04</t>
+          <t>68.02.04</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (25%): 'Teatrul Gong' vs 'Institutii publice de spectacole si conc'</t>
+          <t>name mismatch vs nomenclator (54%): 'Asistenta Sociala - Căminul pentru perso' vs 'Asistenta acordata persoanelor in varsta'</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -25058,37 +24997,37 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>67.02.03.04</t>
+          <t>68.02.05.02</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>duplicate of p18 with different values</t>
+          <t>name mismatch vs nomenclator (48%): 'Drepturile persoanelor si asistentilor p' vs 'Asistenta sociala  in  caz de invalidita'</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C165" t="n">
         <v>18</v>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>67.02.03.30</t>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'SP Managementul Integrat pentru Ecosiste' vs 'Alte servicii culturale'</t>
+          <t>unparseable cell '155.698,45 7.222,00' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -25108,19 +25047,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>67.02.05.03</t>
+          <t>70.02.50</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Intretinere gradini publice, parcuri, zo'</t>
+          <t>name mismatch vs nomenclator (26%): 'Total capitol ,din care :' vs 'Alte servicii în domeniile locuintelor, '</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -25133,19 +25072,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>67.02.05.03</t>
+          <t>70.02.05</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>duplicate of p18 with different values</t>
+          <t>name mismatch vs nomenclator (49%): 'SP Salubrizare, Protecția Mediului și Ad' vs 'Alimentare cu apa si amenajari hidrotehn'</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -25154,16 +25093,16 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>67.02.05.01</t>
+          <t>70.02.50</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'Finanțare programe sportive' vs 'Sport'</t>
+          <t>duplicate of p18 with different values</t>
         </is>
       </c>
     </row>
@@ -25179,23 +25118,23 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>67.02.50</t>
+          <t>70.02.50</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (26%): 'Agenda comunitatii' vs 'Alte servicii în domeniile culturii, rec'</t>
+          <t>name mismatch vs nomenclator (48%): 'Alte subventii si transferuri pentru inv' vs 'Alte servicii în domeniile locuintelor, '</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -25204,16 +25143,16 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>67.02.05.02</t>
+          <t>70.02.50</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (26%): 'Fond destinat activității de tineret, di' vs 'Tineret'</t>
+          <t>duplicate of p18 with different values</t>
         </is>
       </c>
     </row>
@@ -25229,23 +25168,23 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>67.02.05.02</t>
+          <t>74.02.05.01</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (23%): 'Agenda educațională' vs 'Tineret'</t>
+          <t>name mismatch vs nomenclator (23%): 'SP Salubrizare, Protecția Mediului și Ad' vs 'Salubritate'</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -25254,16 +25193,16 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>68.02.10</t>
+          <t>74.02.05.01</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'Cheltuieli de personal' vs 'Ajutoare pentru locuinte'</t>
+          <t>duplicate of p19 with different values</t>
         </is>
       </c>
     </row>
@@ -25279,239 +25218,14 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>68.02.04</t>
+          <t>74.02.06</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (54%): 'Asistenta Sociala - Căminul pentru perso' vs 'Asistenta acordata persoanelor in varsta'</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C174" t="n">
-        <v>18</v>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>68.02.05.02</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (48%): 'Drepturile persoanelor si asistentilor p' vs 'Asistenta sociala  in  caz de invalidita'</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C175" t="n">
-        <v>18</v>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>70.02.50</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (26%): 'Total capitol ,din care :' vs 'Alte servicii în domeniile locuintelor, '</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C176" t="n">
-        <v>18</v>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>70.02.05</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (49%): 'SP Salubrizare, Protecția Mediului și Ad' vs 'Alimentare cu apa si amenajari hidrotehn'</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C177" t="n">
-        <v>19</v>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>70.02.50</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>duplicate of p18 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>19</v>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>70.02.50</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (48%): 'Alte subventii si transferuri pentru inv' vs 'Alte servicii în domeniile locuintelor, '</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C179" t="n">
-        <v>19</v>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>70.02.50</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>duplicate of p18 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
-        <v>19</v>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>74.02.05.01</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (23%): 'SP Salubrizare, Protecția Mediului și Ad' vs 'Salubritate'</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C181" t="n">
-        <v>19</v>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>74.02.05.01</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>duplicate of p19 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C182" t="n">
-        <v>19</v>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>74.02.06</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (40%): 'Canalizare' vs 'Canalizarea si tratarea apelor reziduale'</t>
         </is>
@@ -25528,7 +25242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -25550,7 +25264,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -25560,60 +25274,230 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>431</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>287</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.59999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>146</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>67.09999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>67.09999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>da82f4bb55c23a81768c06c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>94d7e3035a2c1cb711c234218973a6623d887be2e9d2350ff0aaee28a1806dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>— Anexa (de la pagina 5)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 5-21, 713 linii</t>
         </is>
